--- a/artfynd/A 17804-2026 artfynd.xlsx
+++ b/artfynd/A 17804-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6906186</v>
+        <v>6906185</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703224.0150791311</v>
+        <v>703224</v>
       </c>
       <c r="R2" t="n">
-        <v>7165461.139860407</v>
+        <v>7165461</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6906187</v>
+        <v>91373382</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenbäcken - Vallnäs, Vb</t>
+          <t>Kvarnbrännans NR, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703226.8247175897</v>
+        <v>703281</v>
       </c>
       <c r="R3" t="n">
-        <v>7165457.877419581</v>
+        <v>7165409</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-08-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +853,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6906185</v>
+        <v>91373379</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken - Vallnäs, Vb</t>
+          <t>tallås V Vorrtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703224.0150791311</v>
+        <v>703164</v>
       </c>
       <c r="R4" t="n">
-        <v>7165461.139860407</v>
+        <v>7165481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-08-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,66 +955,66 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91373379</v>
+        <v>6906186</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>tallås V Vorrtjärnen, Vb</t>
+          <t>Stenbäcken - Vallnäs, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703164.3930963605</v>
+        <v>703224</v>
       </c>
       <c r="R5" t="n">
-        <v>7165480.87047893</v>
+        <v>7165461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,71 +1057,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91373380</v>
+        <v>104331215</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>tallås V Vorrtjärnen, Vb</t>
+          <t>V Vorrtjärnen, Risliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703183.2524936178</v>
+        <v>703254</v>
       </c>
       <c r="R6" t="n">
-        <v>7165482.995756824</v>
+        <v>7165480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,22 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104331216</v>
+        <v>6906187</v>
       </c>
       <c r="B7" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,34 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>V Vorrtjärnen, Risliden, Vb</t>
+          <t>Stenbäcken - Vallnäs, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703248.0294329217</v>
+        <v>703227</v>
       </c>
       <c r="R7" t="n">
-        <v>7165483.020266864</v>
+        <v>7165458</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,22 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,40 +1251,30 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104331213</v>
+        <v>6906188</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1393,14 +1298,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>V Vorrtjärnen, Risliden, Vb</t>
+          <t>Stenbäcken - Vallnäs, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703272.3960917958</v>
+        <v>703258</v>
       </c>
       <c r="R8" t="n">
-        <v>7165467.399402304</v>
+        <v>7165421</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,22 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,27 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104331215</v>
+        <v>104331167</v>
       </c>
       <c r="B9" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703254.278519489</v>
+        <v>703250</v>
       </c>
       <c r="R9" t="n">
-        <v>7165479.988230755</v>
+        <v>7165493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,19 +1432,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104331212</v>
+        <v>104331168</v>
       </c>
       <c r="B10" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>703286.7640445243</v>
+        <v>703273</v>
       </c>
       <c r="R10" t="n">
-        <v>7165433.424382295</v>
+        <v>7165477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,21 +1529,11 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1677,11 +1542,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1698,19 +1558,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104331167</v>
+        <v>104331169</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1738,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703249.9475551131</v>
+        <v>703277</v>
       </c>
       <c r="R11" t="n">
-        <v>7165493.0691056</v>
+        <v>7165473</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,19 +1626,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,19 +1655,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104331168</v>
+        <v>104331170</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1850,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703273.4542885395</v>
+        <v>703284</v>
       </c>
       <c r="R12" t="n">
-        <v>7165477.390717506</v>
+        <v>7165452</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,19 +1723,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,19 +1752,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104331169</v>
+        <v>104331171</v>
       </c>
       <c r="B13" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1958,14 +1783,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>V Vorrtjärnen, Risliden, Vb</t>
+          <t>Risliden S Vorrtjärnen, Kvarnbrännan NR, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703277.181356806</v>
+        <v>703303</v>
       </c>
       <c r="R13" t="n">
-        <v>7165473.327140177</v>
+        <v>7165421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,19 +1820,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,19 +1849,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104331214</v>
+        <v>104331172</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2070,14 +1880,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>V Vorrtjärnen, Risliden, Vb</t>
+          <t>Risliden S Vorrtjärnen, Kvarnbrännan NR, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703264.5407960119</v>
+        <v>703307</v>
       </c>
       <c r="R14" t="n">
-        <v>7165475.068389951</v>
+        <v>7165417</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,19 +1917,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,19 +1946,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104331170</v>
+        <v>104331173</v>
       </c>
       <c r="B15" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2182,14 +1977,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>V Vorrtjärnen, Risliden, Vb</t>
+          <t>Risliden S Vorrtjärnen, Kvarnbrännan NR, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703283.7786996611</v>
+        <v>703314</v>
       </c>
       <c r="R15" t="n">
-        <v>7165452.202823495</v>
+        <v>7165410</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,19 +2014,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,19 +2043,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104331217</v>
+        <v>104331213</v>
       </c>
       <c r="B16" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2298,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703226.9846108205</v>
+        <v>703272</v>
       </c>
       <c r="R16" t="n">
-        <v>7165513.528459724</v>
+        <v>7165467</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,19 +2111,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,6 +2137,1108 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104331214</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>V Vorrtjärnen, Risliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>703265</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7165475</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104331217</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>V Vorrtjärnen, Risliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>703227</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7165514</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>91373380</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>tallås V Vorrtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>703183</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7165483</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104331211</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>V Vorrtjärnen, Risliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>703290</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7165428</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>91373374</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kvarnbrännans NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>703148</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7165418</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>91373377</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kvarnbrännans NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>703148</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7165418</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104331212</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>V Vorrtjärnen, Risliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>703287</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7165433</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104331216</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>V Vorrtjärnen, Risliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>703248</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7165483</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>91373375</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kvarnbrännans NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>703148</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7165418</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>91373381</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kvarnbrännans NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>703281</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7165409</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>91373376</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kvarnbrännans NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>703148</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7165418</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17804-2026 artfynd.xlsx
+++ b/artfynd/A 17804-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6906185</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91373382</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91373379</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6906186</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331215</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6906187</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6906188</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331167</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331168</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331169</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331170</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331171</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331172</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331173</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331213</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331214</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331217</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91373380</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331211</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91373374</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91373377</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331212</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2933,6 +3048,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104331216</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91373375</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3137,6 +3262,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91373381</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3239,8 +3369,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91373376</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>